--- a/Configs/GameConfig/Datas/wave.xlsx
+++ b/Configs/GameConfig/Datas/wave.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,11 @@
           <t>spawnStrategies</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>skipBoss</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -479,77 +484,91 @@
           <t>(list#sep=;),(list#sep=,),float</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>##group</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>本期显式跳过 Boss</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>##</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>每波怪物数</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Boss波次号</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Boss出现概率</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>生成策略权重</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>生成策略表</t>
+          <t>##group</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>每波怪物数</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Boss波次号</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Boss出现概率</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>生成策略权重</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>生成策略表</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
           <t>10,11,12,13,15,16,18,19,21,24,26,29,31,35,38,42,46,51,56,61</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>3,6,9,12,15,20</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>0.1,0.2,0.3,0.5,0.9,1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>5,2,3</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1;1.1,1.2,1.3,1.2,1.3,1.7,2,1,1.5,1,1,1,1,1,1,1,1,1,1,1;1,1,1.5,1,1.8,2,1,1,2,1,1,1.3,1,1,1.4,1,1,1.5,1,1</t>
         </is>
+      </c>
+      <c r="G6" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/wave.xlsx
+++ b/Configs/GameConfig/Datas/wave.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>skipBoss</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>activePlanId</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -489,6 +494,11 @@
           <t>bool</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -496,9 +506,39 @@
           <t>##</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>【deprecated】旧字段，不再驱动有限波次</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>【deprecated】旧字段，不再驱动有限波次</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>【deprecated】旧字段，不再驱动有限波次</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>【deprecated】旧字段，不再驱动有限波次</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>生成策略表，仅由逐波 strategyProfile 显式引用</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>本期显式跳过 Boss</t>
+          <t>【deprecated】旧字段，不再驱动有限波次</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>当前生效的波次计划ID</t>
         </is>
       </c>
     </row>
@@ -508,6 +548,11 @@
           <t>##group</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -569,6 +614,11 @@
       </c>
       <c r="G6" t="b">
         <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/wave.xlsx
+++ b/Configs/GameConfig/Datas/wave.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R82b45f55eba8454e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra8dc08fb3bf84c20"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -376,9 +376,7 @@
       <x:c r="H1" t="str">
         <x:v>spawnStrategies</x:v>
       </x:c>
-      <x:c r="I1" t="str">
-        <x:v>skipBoss</x:v>
-      </x:c>
+      <x:c r="I1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
@@ -405,36 +403,34 @@
       <x:c r="H2" t="str">
         <x:v>(list#sep=;),(list#sep=,),float</x:v>
       </x:c>
-      <x:c r="I2" t="str">
-        <x:v>bool</x:v>
-      </x:c>
+      <x:c r="I2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B3"/>
+      <x:c r="B3" t="str">
+        <x:v>占位</x:v>
+      </x:c>
       <x:c r="C3" t="str">
-        <x:v>当前生效的波次计划ID</x:v>
+        <x:v>当前启用的波次计划 ID，必须能在 wave_plan.Id 中找到</x:v>
       </x:c>
       <x:c r="D3" t="str">
-        <x:v>【deprecated】旧字段，不再驱动有限波次</x:v>
+        <x:v>已废弃，不再决定波次内容</x:v>
       </x:c>
       <x:c r="E3" t="str">
-        <x:v>【deprecated】旧字段，不再驱动有限波次</x:v>
+        <x:v>已废弃</x:v>
       </x:c>
       <x:c r="F3" t="str">
-        <x:v>【deprecated】旧字段，不再驱动有限波次</x:v>
+        <x:v>已废弃</x:v>
       </x:c>
       <x:c r="G3" t="str">
-        <x:v>【deprecated】旧字段，不再驱动有限波次</x:v>
+        <x:v>已废弃</x:v>
       </x:c>
       <x:c r="H3" t="str">
-        <x:v>生成策略表，仅由逐波 strategyProfile 显式引用</x:v>
-      </x:c>
-      <x:c r="I3" t="str">
-        <x:v>【deprecated】旧字段，不再驱动有限波次</x:v>
-      </x:c>
+        <x:v>生成策略权重二维表，wave_plan.strategyProfile 是这里的行索引（从 0 起）</x:v>
+      </x:c>
+      <x:c r="I3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
@@ -455,27 +451,13 @@
       <x:c r="A5" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B5" t="str">
-        <x:v>ID(主键)</x:v>
-      </x:c>
-      <x:c r="C5" t="str">
-        <x:v>当前生效的波次计划ID(外键)</x:v>
-      </x:c>
-      <x:c r="D5" t="str">
-        <x:v>每波怪物数</x:v>
-      </x:c>
-      <x:c r="E5" t="str">
-        <x:v>Boss波次号</x:v>
-      </x:c>
-      <x:c r="F5" t="str">
-        <x:v>Boss出现概率</x:v>
-      </x:c>
-      <x:c r="G5" t="str">
-        <x:v>生成策略权重</x:v>
-      </x:c>
-      <x:c r="H5" t="str">
-        <x:v>生成策略表</x:v>
-      </x:c>
+      <x:c r="B5"/>
+      <x:c r="C5"/>
+      <x:c r="D5"/>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
       <x:c r="I5"/>
     </x:row>
     <x:row r="6">
@@ -501,9 +483,7 @@
       <x:c r="H6" t="str">
         <x:v>1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1;1.1,1.2,1.3,1.2,1.3,1.7,2,1,1.5,1,1,1,1,1,1,1,1,1,1,1;1,1,1.5,1,1.8,2,1,1,2,1,1,1.3,1,1,1.4,1,1,1.5,1,1</x:v>
       </x:c>
-      <x:c r="I6" s="1" t="b">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="I6"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
